--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4d22fa645f646fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra98d5f312f164a45"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra98d5f312f164a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R889925d361314741"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R889925d361314741"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde93af38dbc847e4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde93af38dbc847e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R189103308f5444f1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R189103308f5444f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc35f2b8061294089"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc35f2b8061294089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R07cfd57097da4e26"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R07cfd57097da4e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82ced0e54fe24c89"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82ced0e54fe24c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2af178c85b3c4390"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2af178c85b3c4390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43682d7ed6c243e2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43682d7ed6c243e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R71d5653ba0c44b20"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R71d5653ba0c44b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdff4e374a0c34a42"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdff4e374a0c34a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58cc1eaac5a94b9b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58cc1eaac5a94b9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13b0c75d06194d8f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13b0c75d06194d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re303d69e7b244654"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re303d69e7b244654"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2da7c6123b8a4183"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2da7c6123b8a4183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7607bf0852d142dd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7607bf0852d142dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R216e893326a740b2"/>
   </x:sheets>
 </x:workbook>
 </file>
